--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
@@ -4998,7 +4998,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
@@ -4998,7 +4998,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
@@ -4998,7 +4998,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
@@ -7064,7 +7064,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
@@ -7064,7 +7064,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251018_201646.xlsx
@@ -4998,7 +4998,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
